--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V505"/>
+  <dimension ref="A1:V541"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1691,11 +1691,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1703,12 +1703,16 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
@@ -4417,20 +4421,28 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>09.09.2026</t>
+        </is>
+      </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4443,7 +4455,7 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -6281,20 +6293,28 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
         <v>7</v>
@@ -6311,7 +6331,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -7529,7 +7549,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -13145,20 +13165,28 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J176" t="b">
-        <v>0</v>
-      </c>
-      <c r="K176" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P176" t="n">
         <v>4</v>
@@ -13175,7 +13203,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
@@ -14951,7 +14979,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -15041,7 +15069,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -15131,7 +15159,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -16135,11 +16163,11 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -16151,12 +16179,16 @@
           <t>24/08/2026</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
       <c r="N211" t="n">
         <v>2</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P211" t="n">
         <v>6</v>
@@ -16229,11 +16261,11 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -16241,12 +16273,16 @@
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>25.08.2026</t>
+        </is>
+      </c>
       <c r="N212" t="n">
         <v>1</v>
       </c>
       <c r="O212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P212" t="n">
         <v>5</v>
@@ -18851,7 +18887,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -23611,11 +23647,11 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J309" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -23623,12 +23659,16 @@
         </is>
       </c>
       <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr"/>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
       <c r="N309" t="n">
         <v>1</v>
       </c>
       <c r="O309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P309" t="n">
         <v>5</v>
@@ -23969,7 +24009,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -23979,11 +24019,11 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -23991,12 +24031,16 @@
         </is>
       </c>
       <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
       <c r="N313" t="n">
         <v>1</v>
       </c>
       <c r="O313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P313" t="n">
         <v>3</v>
@@ -24059,7 +24103,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -24149,7 +24193,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -24245,11 +24289,11 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J316" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
@@ -24257,12 +24301,16 @@
         </is>
       </c>
       <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>28.08.2026</t>
+        </is>
+      </c>
       <c r="N316" t="n">
         <v>1</v>
       </c>
       <c r="O316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P316" t="n">
         <v>0</v>
@@ -24387,7 +24435,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -24465,7 +24513,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -24741,11 +24789,11 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
@@ -24753,12 +24801,16 @@
         </is>
       </c>
       <c r="L322" t="inlineStr"/>
-      <c r="M322" t="inlineStr"/>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
       <c r="N322" t="n">
         <v>1</v>
       </c>
       <c r="O322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P322" t="n">
         <v>7</v>
@@ -24831,11 +24883,11 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
@@ -24843,12 +24895,16 @@
         </is>
       </c>
       <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>26.08.2026</t>
+        </is>
+      </c>
       <c r="N323" t="n">
         <v>1</v>
       </c>
       <c r="O323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P323" t="n">
         <v>3</v>
@@ -25572,15 +25628,23 @@
           <t>1729927</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>087756</t>
+        </is>
+      </c>
       <c r="C333" t="inlineStr">
         <is>
           <t>TUNEIRASDOOESTE</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>1.812,196</t>
+        </is>
+      </c>
       <c r="E333" t="n">
-        <v>0</v>
+        <v>1812.196</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -25592,7 +25656,11 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr"/>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>R$135.864,68</t>
+        </is>
+      </c>
       <c r="I333" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -25613,7 +25681,11 @@
       <c r="P333" t="n">
         <v>2</v>
       </c>
-      <c r="Q333" t="inlineStr"/>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>AES 87756 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
       <c r="R333" t="inlineStr">
         <is>
           <t>1729927 - ALNU392492026 - TAPEJARA</t>
@@ -25621,12 +25693,20 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="T333" t="inlineStr"/>
+          <t>pasta, ae</t>
+        </is>
+      </c>
+      <c r="T333" t="inlineStr">
+        <is>
+          <t>⚠ AE '087756' em múltiplos projetos: 1729927, 1731203, 1731279, 1736579</t>
+        </is>
+      </c>
       <c r="U333" t="inlineStr"/>
-      <c r="V333" t="inlineStr"/>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87756 4600026463 HAGAP.pdf', 'ae': '087756'}]</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -26085,7 +26165,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -26385,7 +26465,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -26471,7 +26551,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -26557,7 +26637,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -26643,7 +26723,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -26729,7 +26809,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -26815,7 +26895,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -26901,7 +26981,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -26983,7 +27063,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -27065,7 +27145,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -27139,7 +27219,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -27221,7 +27301,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -27767,7 +27847,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -27853,7 +27933,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -27939,7 +28019,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -28025,7 +28105,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -28111,7 +28191,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -28197,7 +28277,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -28283,7 +28363,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -29179,7 +29259,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -30313,7 +30393,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -30583,11 +30663,19 @@
       <c r="J400" t="b">
         <v>0</v>
       </c>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>18/08/2026</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O400" t="n">
         <v>0</v>
@@ -30607,7 +30695,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>ae, pasta</t>
+          <t>ae, pasta, medicao</t>
         </is>
       </c>
       <c r="T400" t="inlineStr">
@@ -31811,7 +31899,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -31897,7 +31985,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -31907,11 +31995,11 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J417" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K417" t="inlineStr">
         <is>
@@ -31919,12 +32007,16 @@
         </is>
       </c>
       <c r="L417" t="inlineStr"/>
-      <c r="M417" t="inlineStr"/>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
       <c r="N417" t="n">
         <v>1</v>
       </c>
       <c r="O417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P417" t="n">
         <v>5</v>
@@ -31983,7 +32075,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -32405,7 +32497,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -32483,7 +32575,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -32561,7 +32653,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -32639,7 +32731,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -32717,7 +32809,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -33039,7 +33131,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -33125,7 +33217,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -33211,7 +33303,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -33297,7 +33389,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -34235,7 +34327,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -36035,7 +36127,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>alerta</t>
+          <t>critico</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -36199,7 +36291,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -36285,7 +36377,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -36371,7 +36463,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -36457,7 +36549,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -36543,7 +36635,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -36629,7 +36721,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -37825,7 +37917,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -37911,7 +38003,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -37997,7 +38089,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -38083,7 +38175,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -38169,7 +38261,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -38711,7 +38803,7 @@
         <v>0</v>
       </c>
       <c r="P503" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q503" t="inlineStr">
         <is>
@@ -38856,6 +38948,3070 @@
       <c r="U505" t="inlineStr"/>
       <c r="V505" t="inlineStr"/>
     </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>1704934</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>087752</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>INDIANOPOLIS</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2.681,733</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>2681.733</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>R$204.777,12</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J506" t="b">
+        <v>0</v>
+      </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
+      <c r="N506" t="n">
+        <v>0</v>
+      </c>
+      <c r="O506" t="n">
+        <v>0</v>
+      </c>
+      <c r="P506" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>AES 87752 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>1704934 e 1722005 - DER</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr"/>
+      <c r="U506" t="inlineStr"/>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87752 4600026463 HAGAP.pdf', 'ae': '087752'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>1731203</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>087756</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>PEROBAL</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>1.812,196</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>1812.196</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>R$135.864,68</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J507" t="b">
+        <v>0</v>
+      </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="n">
+        <v>0</v>
+      </c>
+      <c r="O507" t="n">
+        <v>0</v>
+      </c>
+      <c r="P507" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>AES 87756 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>1731203 - PO2027 - ALNU388272026 - BRT</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>⚠ AE '087756' em múltiplos projetos: 1729927, 1731203, 1731279, 1736579</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr"/>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87756 4600026463 HAGAP.pdf', 'ae': '087756'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>1731279</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>087756</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>CIANORTE</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>1.812,196</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>1812.196</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>R$135.864,68</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J508" t="b">
+        <v>0</v>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
+      <c r="N508" t="n">
+        <v>0</v>
+      </c>
+      <c r="O508" t="n">
+        <v>0</v>
+      </c>
+      <c r="P508" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>AES 87756 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>1731279 - CIANORTE - TRAVESSIA - LNNU343002025</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>⚠ AE '087756' em múltiplos projetos: 1729927, 1731203, 1731279, 1736579</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr"/>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87756 4600026463 HAGAP.pdf', 'ae': '087756'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>1736579</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>087756</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>CRUZEIRODOOESTE</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>1.812,196</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>1812.196</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>R$135.864,68</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J509" t="b">
+        <v>0</v>
+      </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
+      <c r="N509" t="n">
+        <v>0</v>
+      </c>
+      <c r="O509" t="n">
+        <v>0</v>
+      </c>
+      <c r="P509" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>AES 87756 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>1736579 LDNU388112026 - BRT - CRUZEIRO DO OESTE</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>⚠ AE '087756' em múltiplos projetos: 1729927, 1731203, 1731279, 1736579</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr"/>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87756 4600026463 HAGAP.pdf', 'ae': '087756'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>1722005</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>087762</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>3.025,157</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>3025.157</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>R$231.000,95</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J510" t="b">
+        <v>0</v>
+      </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="n">
+        <v>0</v>
+      </c>
+      <c r="O510" t="n">
+        <v>0</v>
+      </c>
+      <c r="P510" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>AES 87762 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr"/>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>⚠ AE '087762' em múltiplos projetos: 1722005, 1736404, 1736719, 1740081, 1740335</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr"/>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87762 4600026463 HAGAP.pdf', 'ae': '087762'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>1736404</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>087762</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>ARARUNA</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>3.025,157</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>3025.157</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>R$231.000,95</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J511" t="b">
+        <v>0</v>
+      </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="n">
+        <v>0</v>
+      </c>
+      <c r="O511" t="n">
+        <v>0</v>
+      </c>
+      <c r="P511" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>AES 87762 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>1736404</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>⚠ AE '087762' em múltiplos projetos: 1722005, 1736404, 1736719, 1740081, 1740335</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr"/>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87762 4600026463 HAGAP.pdf', 'ae': '087762'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>1736719</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>087762</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>PEROLA</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>3.025,157</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>3025.157</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>R$231.000,95</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J512" t="b">
+        <v>0</v>
+      </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="n">
+        <v>0</v>
+      </c>
+      <c r="O512" t="n">
+        <v>0</v>
+      </c>
+      <c r="P512" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>AES 87762 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>1736719 LDNU389052026 - PEROLA - BRT</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>⚠ AE '087762' em múltiplos projetos: 1722005, 1736404, 1736719, 1740081, 1740335</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr"/>
+      <c r="V512" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87762 4600026463 HAGAP.pdf', 'ae': '087762'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>1740081</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>087762</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>S SUBESTAÇÕES ALIMENTADORES VÍNCULOS</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>3.025,157</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>3025.157</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>R$231.000,95</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J513" t="b">
+        <v>0</v>
+      </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="n">
+        <v>0</v>
+      </c>
+      <c r="O513" t="n">
+        <v>0</v>
+      </c>
+      <c r="P513" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>AES 87762 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>1740081 ALNU390772026 BRT</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>⚠ AE '087762' em múltiplos projetos: 1722005, 1736404, 1736719, 1740081, 1740335</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr"/>
+      <c r="V513" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87762 4600026463 HAGAP.pdf', 'ae': '087762'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>1740335</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>087762</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>NOVAOLIMPIA</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>3.025,157</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>3025.157</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>R$231.000,95</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J514" t="b">
+        <v>0</v>
+      </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
+      <c r="N514" t="n">
+        <v>0</v>
+      </c>
+      <c r="O514" t="n">
+        <v>0</v>
+      </c>
+      <c r="P514" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>AES 87762 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>1740335 PO2027 - ALNU390812026 - 100000049555 - BRT</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>⚠ AE '087762' em múltiplos projetos: 1722005, 1736404, 1736719, 1740081, 1740335</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr"/>
+      <c r="V514" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87762 4600026463 HAGAP.pdf', 'ae': '087762'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>1704872</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>087763</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>RONDON</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>4.232,753</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>4232.753</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>R$323.213,01</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J515" t="b">
+        <v>0</v>
+      </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="n">
+        <v>0</v>
+      </c>
+      <c r="O515" t="n">
+        <v>0</v>
+      </c>
+      <c r="P515" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>AES 87763 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>1704872 - DER</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>⚠ AE '087763' em múltiplos projetos: 1704872, 1704892</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr"/>
+      <c r="V515" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87763 4600026463 HAGAP.pdf', 'ae': '087763'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>1704892</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>087763</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>RONDON</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>4.232,753</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>4232.753</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>R$323.213,01</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J516" t="b">
+        <v>0</v>
+      </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
+      <c r="N516" t="n">
+        <v>0</v>
+      </c>
+      <c r="O516" t="n">
+        <v>0</v>
+      </c>
+      <c r="P516" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>AES 87763 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>1704892 - DER</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>⚠ AE '087763' em múltiplos projetos: 1704872, 1704892</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr"/>
+      <c r="V516" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87763 4600026463 HAGAP.pdf', 'ae': '087763'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>1737781</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>DEASCHORK AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J517" t="b">
+        <v>0</v>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="n">
+        <v>0</v>
+      </c>
+      <c r="O517" t="n">
+        <v>0</v>
+      </c>
+      <c r="P517" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>1737781 01.20265007505582 - GILBERTO ALVES DA SILVA 26-10-2026</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr"/>
+      <c r="V517" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>1738687</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>ARAUJO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J518" t="b">
+        <v>0</v>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="n">
+        <v>0</v>
+      </c>
+      <c r="O518" t="n">
+        <v>0</v>
+      </c>
+      <c r="P518" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>1738687 01.20265027388718 - EDUARDO DE OLIVEIRA STOFFEL 26-10-2026</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr"/>
+      <c r="V518" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>1739815</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>CIANORTE</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J519" t="b">
+        <v>0</v>
+      </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
+      <c r="N519" t="n">
+        <v>0</v>
+      </c>
+      <c r="O519" t="n">
+        <v>0</v>
+      </c>
+      <c r="P519" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>1739815 01.20265124309512 - ADRIANA DAS GRACAS DA SILVA LAURENTE 30-10-2026</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr"/>
+      <c r="V519" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>1738727</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J520" t="b">
+        <v>0</v>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="n">
+        <v>0</v>
+      </c>
+      <c r="O520" t="n">
+        <v>0</v>
+      </c>
+      <c r="P520" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>1738727 01.20265101300777 - WILLIAN SERGIO DE MELO 26-10-2026</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr"/>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>1739810</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J521" t="b">
+        <v>0</v>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
+      <c r="N521" t="n">
+        <v>0</v>
+      </c>
+      <c r="O521" t="n">
+        <v>0</v>
+      </c>
+      <c r="P521" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>1739810 01.20265165782868 - IGREJA EVANGELICA ASSEMBLEIA DE DEUS EM NOVA OLIMPIA PR 28-12-2026</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr"/>
+      <c r="V521" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>1743087</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>ARAUJO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J522" t="b">
+        <v>0</v>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="n">
+        <v>0</v>
+      </c>
+      <c r="O522" t="n">
+        <v>0</v>
+      </c>
+      <c r="P522" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q522" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R522" t="inlineStr">
+        <is>
+          <t>1743087 01.20265430302564 - DOUGLAS NATAN DIAS GOMES 28-12-2026</t>
+        </is>
+      </c>
+      <c r="S522" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T522" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U522" t="inlineStr"/>
+      <c r="V522" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>1743770</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J523" t="b">
+        <v>0</v>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="n">
+        <v>0</v>
+      </c>
+      <c r="O523" t="n">
+        <v>0</v>
+      </c>
+      <c r="P523" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q523" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>1743770 01.20265484557040 - PLUMA AGROAVICOLA LTDA 26-10-2026</t>
+        </is>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T523" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U523" t="inlineStr"/>
+      <c r="V523" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>1739821</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>087764</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>669,949</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>669.949</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>20/10/2026</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>R$43.203,36</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J524" t="b">
+        <v>0</v>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="n">
+        <v>0</v>
+      </c>
+      <c r="O524" t="n">
+        <v>0</v>
+      </c>
+      <c r="P524" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q524" t="inlineStr">
+        <is>
+          <t>AES 87764 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R524" t="inlineStr">
+        <is>
+          <t>1739821 01.20265197386167 - MARCIO PEREIRA VALENTINI 30-10-2026</t>
+        </is>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T524" t="inlineStr">
+        <is>
+          <t>⚠ AE '087764' em múltiplos projetos: 1737781, 1738687, 1739815, 1738727, 1739810, 1743087, 1743770, 1739821</t>
+        </is>
+      </c>
+      <c r="U524" t="inlineStr"/>
+      <c r="V524" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87764 4600026463 HAGAP.pdf', 'ae': '087764'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>1684782</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>087765</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>198,521</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>198.521</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>R$15.159,06</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J525" t="b">
+        <v>0</v>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="n">
+        <v>0</v>
+      </c>
+      <c r="O525" t="n">
+        <v>0</v>
+      </c>
+      <c r="P525" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q525" t="inlineStr">
+        <is>
+          <t>AES 87765 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>1684782 - MODELO INDUSTRIA E COMERCIO DE LATICINIOS LTDA</t>
+        </is>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T525" t="inlineStr"/>
+      <c r="U525" t="inlineStr"/>
+      <c r="V525" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87765 4600026463 HAGAP.pdf', 'ae': '087765'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>1736033</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>ANUNCIACAO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J526" t="b">
+        <v>0</v>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="n">
+        <v>0</v>
+      </c>
+      <c r="O526" t="n">
+        <v>0</v>
+      </c>
+      <c r="P526" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q526" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R526" t="inlineStr">
+        <is>
+          <t>1736033 01.20264887151673 - JUVENI AGUINELO DA SILVA 31.12</t>
+        </is>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T526" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U526" t="inlineStr"/>
+      <c r="V526" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>1737787</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>CASTRO AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J527" t="b">
+        <v>0</v>
+      </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
+      <c r="N527" t="n">
+        <v>0</v>
+      </c>
+      <c r="O527" t="n">
+        <v>0</v>
+      </c>
+      <c r="P527" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q527" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R527" t="inlineStr">
+        <is>
+          <t>1737787 01.20265011889386 - SIDNEI FORMENTINI 03.11</t>
+        </is>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T527" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U527" t="inlineStr"/>
+      <c r="V527" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>1738371</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>LEMOS AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J528" t="b">
+        <v>0</v>
+      </c>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="n">
+        <v>0</v>
+      </c>
+      <c r="O528" t="n">
+        <v>0</v>
+      </c>
+      <c r="P528" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q528" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R528" t="inlineStr">
+        <is>
+          <t>1738371 01.20265056663418 - CLOVIS PEDROCHE 03.11</t>
+        </is>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T528" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U528" t="inlineStr"/>
+      <c r="V528" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>1738724</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>DEFRANCISCOALVES CENTRO</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J529" t="b">
+        <v>0</v>
+      </c>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="n">
+        <v>0</v>
+      </c>
+      <c r="O529" t="n">
+        <v>0</v>
+      </c>
+      <c r="P529" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q529" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R529" t="inlineStr">
+        <is>
+          <t>1738724 01.20265033085626 - MUNICIPIO DE FRANCISCO ALVES 30-08-2027</t>
+        </is>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T529" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U529" t="inlineStr"/>
+      <c r="V529" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>1739375</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J530" t="b">
+        <v>0</v>
+      </c>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="n">
+        <v>0</v>
+      </c>
+      <c r="O530" t="n">
+        <v>0</v>
+      </c>
+      <c r="P530" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q530" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R530" t="inlineStr">
+        <is>
+          <t>1739375 01.20265137993401 - JOSE CARLOS RICOLDO - falta projeto MARCELO FRARE 01-03-2027</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U530" t="inlineStr"/>
+      <c r="V530" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>1739813</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J531" t="b">
+        <v>0</v>
+      </c>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
+      <c r="N531" t="n">
+        <v>0</v>
+      </c>
+      <c r="O531" t="n">
+        <v>0</v>
+      </c>
+      <c r="P531" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q531" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R531" t="inlineStr">
+        <is>
+          <t>1739813 01.20265169231568 - DIVA APARECIDA PERISSATO MAGRE 31.12</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U531" t="inlineStr"/>
+      <c r="V531" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>1741037</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J532" t="b">
+        <v>0</v>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="n">
+        <v>0</v>
+      </c>
+      <c r="O532" t="n">
+        <v>0</v>
+      </c>
+      <c r="P532" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q532" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R532" t="inlineStr">
+        <is>
+          <t>1741037 01.20265211630923 - ALEX PAULO DE BARROS 31.12</t>
+        </is>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T532" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U532" t="inlineStr"/>
+      <c r="V532" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>1740967</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>087822</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>824,788</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>824.788</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>27/10/2026</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>R$57.310,03</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J533" t="b">
+        <v>0</v>
+      </c>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="n">
+        <v>0</v>
+      </c>
+      <c r="O533" t="n">
+        <v>0</v>
+      </c>
+      <c r="P533" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>AES 87822 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>1740967 01.20265226827882 - ELIANDRO DOS SANTOS SANTANA 04.01.27</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>⚠ AE '087822' em múltiplos projetos: 1736033, 1737787, 1738371, 1738724, 1739375, 1739813, 1741037, 1740967</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr"/>
+      <c r="V533" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87822 4600026463 HAGAP.pdf', 'ae': '087822'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>1739071</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>087845</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>LIBERAÇÃODOPEPVIA</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>1.061,006</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>1061.006</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>R$81.018,41</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J534" t="b">
+        <v>0</v>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="n">
+        <v>0</v>
+      </c>
+      <c r="O534" t="n">
+        <v>0</v>
+      </c>
+      <c r="P534" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>AES 87845 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>1739071 - ALOT385332026</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr"/>
+      <c r="U534" t="inlineStr"/>
+      <c r="V534" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87845 4600026463 HAGAP.pdf', 'ae': '087845'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>1718931</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>087846</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>DEDOURADINA</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>3.080,785</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>3080.785</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>R$235.248,73</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J535" t="b">
+        <v>0</v>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
+      <c r="N535" t="n">
+        <v>0</v>
+      </c>
+      <c r="O535" t="n">
+        <v>0</v>
+      </c>
+      <c r="P535" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>AES 87846 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>1718931 - 1718955 01.20264175336152 - MUNICIPIO DE DOURADINA 25062027</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>⚠ AE '087846' em múltiplos projetos: 1718931, 1718955</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr"/>
+      <c r="V535" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87846 4600026463 HAGAP.pdf', 'ae': '087846'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>1718955</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>087846</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>3.080,785</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>3080.785</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>R$235.248,73</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J536" t="b">
+        <v>0</v>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
+      <c r="N536" t="n">
+        <v>0</v>
+      </c>
+      <c r="O536" t="n">
+        <v>0</v>
+      </c>
+      <c r="P536" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>AES 87846 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr"/>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>⚠ AE '087846' em múltiplos projetos: 1718931, 1718955</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr"/>
+      <c r="V536" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87846 4600026463 HAGAP.pdf', 'ae': '087846'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>1739957</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>087855</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>MOREIRA AZEVEDO EXECUÇÃODECAMPO</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>483,108</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>483.108</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>R$36.890,12</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J537" t="b">
+        <v>0</v>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
+      <c r="N537" t="n">
+        <v>0</v>
+      </c>
+      <c r="O537" t="n">
+        <v>0</v>
+      </c>
+      <c r="P537" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>AES 87855 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>1739957 - LDNU390752026 BRT 200A</t>
+        </is>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>⚠ AE '087855' em múltiplos projetos: 1739957, 1740397</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr"/>
+      <c r="V537" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87855 4600026463 HAGAP.pdf', 'ae': '087855'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>1740397</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>087855</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>UMUARAMA</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>483,108</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>483.108</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>R$36.890,12</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J538" t="b">
+        <v>0</v>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
+      <c r="N538" t="n">
+        <v>0</v>
+      </c>
+      <c r="O538" t="n">
+        <v>0</v>
+      </c>
+      <c r="P538" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>AES 87855 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>1740397 LDNU392642026 - 100000049549 - BRT - UMU</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>⚠ AE '087855' em múltiplos projetos: 1739957, 1740397</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr"/>
+      <c r="V538" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87855 4600026463 HAGAP.pdf', 'ae': '087855'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>1733740</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>087903</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>132,875</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>132.875</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>R$9.000,17</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J539" t="b">
+        <v>0</v>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
+      <c r="N539" t="n">
+        <v>0</v>
+      </c>
+      <c r="O539" t="n">
+        <v>0</v>
+      </c>
+      <c r="P539" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>AES 87903 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>1733740 01.20264640008186 - PAULA CAROLINE SILVA BONOTTO - SO TEM CROQUI 16-02-2027</t>
+        </is>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>⚠ AE '087903' em múltiplos projetos: 1733740, 1742497</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr"/>
+      <c r="V539" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87903 4600026463 HAGAP.pdf', 'ae': '087903'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>1742497</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>087903</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>132,875</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>132.875</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>R$9.000,17</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J540" t="b">
+        <v>0</v>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
+      <c r="N540" t="n">
+        <v>0</v>
+      </c>
+      <c r="O540" t="n">
+        <v>0</v>
+      </c>
+      <c r="P540" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>AES 87903 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>1742497 01.20265291637210 - CLAUDIO VALDENIR DA SILVA 06-11-2026</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>⚠ AE '087903' em múltiplos projetos: 1733740, 1742497</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr"/>
+      <c r="V540" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87903 4600026463 HAGAP.pdf', 'ae': '087903'}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>1739077</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>087904</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>FORMOSA DO OESTE</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>124,437</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>124.437</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>09/12/2026</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>R$9.502,00</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J541" t="b">
+        <v>0</v>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
+      <c r="N541" t="n">
+        <v>0</v>
+      </c>
+      <c r="O541" t="n">
+        <v>0</v>
+      </c>
+      <c r="P541" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>AES 87904 4600026463 HAGAP.pdf</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>1739077 - ALOT385332026</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>ae, pasta</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr"/>
+      <c r="U541" t="inlineStr"/>
+      <c r="V541" t="inlineStr">
+        <is>
+          <t>[{'arquivo': 'AES 87904 4600026463 HAGAP.pdf', 'ae': '087904'}]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V541"/>
+  <dimension ref="A1:V550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7094,10 +7094,14 @@
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -18615,24 +18619,32 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
           <t>06/08/2026</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
       <c r="N243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P243" t="n">
         <v>5</v>
@@ -24371,20 +24383,28 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J317" t="b">
-        <v>0</v>
-      </c>
-      <c r="K317" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
       <c r="N317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P317" t="n">
         <v>0</v>
@@ -24397,7 +24417,7 @@
       <c r="R317" t="inlineStr"/>
       <c r="S317" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -24699,24 +24719,32 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J321" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
           <t>17/08/2026</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
       <c r="N321" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P321" t="n">
         <v>6</v>
@@ -26175,20 +26203,28 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J341" t="b">
-        <v>0</v>
-      </c>
-      <c r="K341" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr"/>
-      <c r="M341" t="inlineStr"/>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
       <c r="N341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P341" t="n">
         <v>0</v>
@@ -26201,7 +26237,7 @@
       <c r="R341" t="inlineStr"/>
       <c r="S341" t="inlineStr">
         <is>
-          <t>ae</t>
+          <t>ae, medicao</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -27847,7 +27883,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -27933,7 +27969,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -28019,7 +28055,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -28105,7 +28141,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -28191,7 +28227,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -28277,7 +28313,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -28363,7 +28399,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -28975,20 +29011,28 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J377" t="b">
-        <v>0</v>
-      </c>
-      <c r="K377" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>21/08/2026</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr"/>
-      <c r="M377" t="inlineStr"/>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
       <c r="N377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P377" t="n">
         <v>5</v>
@@ -29005,7 +29049,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>pasta, ae</t>
+          <t>pasta, ae, medicao</t>
         </is>
       </c>
       <c r="T377" t="inlineStr"/>
@@ -29259,7 +29303,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -30393,7 +30437,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -33131,7 +33175,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -33217,7 +33261,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -33303,7 +33347,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -33471,7 +33515,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -33557,7 +33601,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -33643,7 +33687,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -33729,7 +33773,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -33819,7 +33863,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -33909,7 +33953,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -33995,7 +34039,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -34081,7 +34125,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -34171,7 +34215,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -36063,24 +36107,32 @@
       <c r="H471" t="inlineStr"/>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="J471" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K471" t="inlineStr">
         <is>
           <t>19/08/2026</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr"/>
-      <c r="M471" t="inlineStr"/>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>19/08/2026</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>18.09.2026</t>
+        </is>
+      </c>
       <c r="N471" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O471" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P471" t="n">
         <v>0</v>
@@ -36127,7 +36179,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>critico</t>
+          <t>vencido</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -38691,7 +38743,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -38777,7 +38829,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
@@ -39913,7 +39965,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -39999,7 +40051,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -40085,7 +40137,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -40171,7 +40223,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
@@ -40257,7 +40309,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
@@ -40343,7 +40395,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -40429,7 +40481,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -40515,7 +40567,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -42012,6 +42064,560 @@
         </is>
       </c>
     </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>1729831</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>CANTELLI AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" t="n">
+        <v>0</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>18.06.2027</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J542" t="b">
+        <v>0</v>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
+      <c r="N542" t="n">
+        <v>0</v>
+      </c>
+      <c r="O542" t="n">
+        <v>0</v>
+      </c>
+      <c r="P542" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q542" t="inlineStr"/>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>1729831 01.20264496342596 - AVELINO ANTONIO DA ROCHA NETO 04-01-2027</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr"/>
+      <c r="U542" t="inlineStr"/>
+      <c r="V542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>1739806</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" t="n">
+        <v>0</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>14.08.2027</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J543" t="b">
+        <v>0</v>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
+      <c r="N543" t="n">
+        <v>0</v>
+      </c>
+      <c r="O543" t="n">
+        <v>0</v>
+      </c>
+      <c r="P543" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q543" t="inlineStr"/>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>1739806 01.20265051844179 - GRASIELI PEREIRA DE PAULA 06-11-2026</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr"/>
+      <c r="U543" t="inlineStr"/>
+      <c r="V543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>1739818</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="n">
+        <v>0</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>24.08.2026</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>vencido</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J544" t="b">
+        <v>0</v>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
+      <c r="N544" t="n">
+        <v>0</v>
+      </c>
+      <c r="O544" t="n">
+        <v>0</v>
+      </c>
+      <c r="P544" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q544" t="inlineStr"/>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>1739818 01.20265182300845 - CONSELHO DE DESENVOLVIMENTO COMUNITARIO DO DISTRITO DE SAO LOURENCO 09-11-2026</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr"/>
+      <c r="U544" t="inlineStr"/>
+      <c r="V544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>1741044</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="n">
+        <v>0</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>R$10.090,61</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J545" t="b">
+        <v>0</v>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
+      <c r="N545" t="n">
+        <v>0</v>
+      </c>
+      <c r="O545" t="n">
+        <v>0</v>
+      </c>
+      <c r="P545" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q545" t="inlineStr"/>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>1741044 01.20265224786670 - L C MORI EMBALAGENS LTDA 03-11-2026</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr"/>
+      <c r="U545" t="inlineStr"/>
+      <c r="V545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>1741045</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" t="n">
+        <v>0</v>
+      </c>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>R$0,00</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J546" t="b">
+        <v>0</v>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
+      <c r="N546" t="n">
+        <v>0</v>
+      </c>
+      <c r="O546" t="n">
+        <v>0</v>
+      </c>
+      <c r="P546" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q546" t="inlineStr"/>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>1741045 01.20265225151470 - KARINA RENATA MOREIRA MAZER 07-01-2027</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr"/>
+      <c r="U546" t="inlineStr"/>
+      <c r="V546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>1741586</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="n">
+        <v>0</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>30.09.2027</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J547" t="b">
+        <v>0</v>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
+      <c r="N547" t="n">
+        <v>0</v>
+      </c>
+      <c r="O547" t="n">
+        <v>0</v>
+      </c>
+      <c r="P547" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q547" t="inlineStr"/>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>1741586 01.20265320955652 - ADEMIR PAULINO FERRARINI 09-11-2026</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr"/>
+      <c r="U547" t="inlineStr"/>
+      <c r="V547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>1743091</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="n">
+        <v>0</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>03.02.2027</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J548" t="b">
+        <v>0</v>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
+      <c r="N548" t="n">
+        <v>0</v>
+      </c>
+      <c r="O548" t="n">
+        <v>0</v>
+      </c>
+      <c r="P548" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q548" t="inlineStr"/>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>1743091 01.20265320460766 - KAUANI RAMOS THE - falta projeto Ticiano 09-11-2026</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr"/>
+      <c r="U548" t="inlineStr"/>
+      <c r="V548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>1743095</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>AZEVEDO</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="n">
+        <v>0</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>31.12.2027</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J549" t="b">
+        <v>0</v>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
+      <c r="N549" t="n">
+        <v>0</v>
+      </c>
+      <c r="O549" t="n">
+        <v>0</v>
+      </c>
+      <c r="P549" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q549" t="inlineStr"/>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>1743095 01.20265373231459 - MARIA ANTONIA DA SILVA 12-11-2026</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr"/>
+      <c r="U549" t="inlineStr"/>
+      <c r="V549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>1744409</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>NOVA TEBAS</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>91,340</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J550" t="b">
+        <v>0</v>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
+      <c r="N550" t="n">
+        <v>0</v>
+      </c>
+      <c r="O550" t="n">
+        <v>0</v>
+      </c>
+      <c r="P550" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q550" t="inlineStr"/>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>1744409 (1706447) TK NOVA TEBAS</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr"/>
+      <c r="U550" t="inlineStr"/>
+      <c r="V550" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
